--- a/AAII_Financials/Quarterly/BLDR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/BLDR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="92">
   <si>
     <t>BLDR</t>
   </si>
@@ -656,543 +656,556 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3862500</v>
+      </c>
+      <c r="E8" s="3">
         <v>3287100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>3357900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>3941200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>4234100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>3657500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3820300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>4232500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>4456300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3891400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>4150900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>4534300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>4528900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3883300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>4357600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>5761500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>6926300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>5681100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>4634800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5508600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>5576700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4173800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2530800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2295500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>1945600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1787000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1763600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1981000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1904500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>1631300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1816000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2118500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2089900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>1700400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1778900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1878900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>1843300</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>1533100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1546900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1746000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2775800</v>
+      </c>
+      <c r="E9" s="3">
         <v>2358100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2355900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2741700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2935000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2542300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2586100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2846200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2993700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2591500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2686000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2953200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2933900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2511900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2872400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>3746700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>4514100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>3848800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>3149000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>3796100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>3993500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3104200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1861600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1724800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1428300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1321600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1287000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1439900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1387400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1189300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1323200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1595700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1593600</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1289400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1347700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1419600</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1382500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1157000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1155300</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>1308900</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1086800</v>
+      </c>
+      <c r="E10" s="3">
         <v>929000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1002000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1199500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1299000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1115200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>1234200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>1386300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>1462700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>1299900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>1464900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1581100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1594900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1371400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>1485200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>2014800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>2412200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>1832300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1485800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1712500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1583200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1069600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>669200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>570700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>517300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>465400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>476600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>541100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>517100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>442000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>492800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>522800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>496300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>411000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>431200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>459300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>460800</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>376100</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>391600</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>437100</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1235,8 +1248,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1357,8 +1371,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1479,8 +1496,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1523,11 +1543,11 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="s">
-        <v>8</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
       </c>
       <c r="S14" s="3" t="s">
         <v>8</v>
@@ -1535,8 +1555,8 @@
       <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
+      <c r="U14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V14" s="3">
         <v>0</v>
@@ -1545,11 +1565,11 @@
         <v>0</v>
       </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>17600</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1565,8 +1585,8 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF14" s="3">
         <v>0</v>
@@ -1592,8 +1612,8 @@
       <c r="AM14" s="3">
         <v>0</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
+      <c r="AN14" s="3">
+        <v>0</v>
       </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
@@ -1601,8 +1621,11 @@
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1610,44 +1633,44 @@
         <v>5200</v>
       </c>
       <c r="E15" s="3">
+        <v>5200</v>
+      </c>
+      <c r="F15" s="3">
         <v>302100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>147500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>145000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>305700</v>
-      </c>
-      <c r="J15" s="3">
-        <v>300</v>
       </c>
       <c r="K15" s="3">
         <v>300</v>
       </c>
       <c r="L15" s="3">
+        <v>300</v>
+      </c>
+      <c r="M15" s="3">
         <v>140400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>337100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>140600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>139000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>136500</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
       <c r="R15" s="3">
         <v>0</v>
       </c>
@@ -1723,8 +1746,11 @@
       <c r="AP15" s="3">
         <v>0</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1764,252 +1790,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>3734000</v>
+      </c>
+      <c r="E17" s="3">
         <v>3270600</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3296100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3712400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3922800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3473100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3516200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3804500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3966900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3517800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3660400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3892600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>3951800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3416100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3831600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>4746900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>5560400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>4817300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>4013000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>4671200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>4896400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>3925800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2316900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2155700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>1816400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1726100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1688400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1851400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1788900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1559400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1725500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1996700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1985300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1648300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1714100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1790200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1752000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1492800</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1496000</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1659700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>128500</v>
+      </c>
+      <c r="E18" s="3">
         <v>16500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>61800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>228800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>311300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>184400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>304100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>428000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>489500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>373600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>490400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>641600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>577100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>467200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>526000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1014600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1365900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>863800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>621800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>837500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>680300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>248000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>213900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>139800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>129200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>60900</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>75200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>129600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>115600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>71900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>90500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>121800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>104600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>52100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>64800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>88700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>91300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>40300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>50900</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>86300</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2052,8 +2085,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2096,8 +2130,8 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R20" s="3">
         <v>0</v>
@@ -2174,496 +2208,511 @@
       <c r="AP20" s="3">
         <v>0</v>
       </c>
+      <c r="AQ20" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E21" s="3">
         <v>21700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>363900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>233600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>458800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>329500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>609800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>428300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>489800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>514000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>827500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>782200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>716000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>603700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>667700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1140200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1483700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>975800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>767600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>977400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>807500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>382300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>243200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>169200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>157700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>90300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>103400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>154000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>139500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>95500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>115700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>146900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>129300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>75000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>87000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>111700</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>115500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>63900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>73800</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>111800</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>76100</v>
+      </c>
+      <c r="E22" s="3">
         <v>74400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>67800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>69300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>72000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>64900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>53100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>54300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>52000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>48300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>46800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>53000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>42100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>42200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>44100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>70700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>40300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>36000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>27800</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>31800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>28900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>28000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>26800</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>51900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>27500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>27800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>29400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>24900</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>29100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>29000</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>26700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>89500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>33800</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>33700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>36200</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>44400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>92300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>52400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-57900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-6000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>159500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>239300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>119500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>251000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>373800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>437500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>325300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>443600</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>591400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>524100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>425100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>483800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>970400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1295200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>822500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>581500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>801500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>652400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>216100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>185000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>111700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>102400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>9000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>47700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>101800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>86300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>47000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>67100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>92700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>75600</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>25400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-24700</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>54800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>57600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>4100</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>6500</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-6000</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>56300</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-37500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>37100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>54300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>23200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>60800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>89000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>93400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>66500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>92900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>140000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>119400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>91300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>99300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>232400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>307900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>182900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>139100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>188300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>155200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>45100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>25800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>23500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>23700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>19700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>11300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>15000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>19400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>19000</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-11000</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>15100</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>19700</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>300</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>100</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>-131500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2784,252 +2833,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E26" s="3">
         <v>-47400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>31500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>122400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>185000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>96300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>190200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>284800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>344100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>258800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>350700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>451500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>404600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>333800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>384500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>738000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>987200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>639600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>442500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>613100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>497200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>172600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>139900</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>85900</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>78900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>41400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>78100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>66600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>35700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>52000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>73300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>23200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-13700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>39800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>37900</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3800</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>6400</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E27" s="3">
         <v>-47400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>31500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>122400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>185000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>96300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>190200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>284800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>344100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>258800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>350700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>451500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>404600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>333800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>384500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>738000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>987200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>639600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>442500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>613100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>497200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>172600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>139900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>85900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>78900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>8800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>41400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>78100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>66600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>35700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>52000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>73300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>23200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-13700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>39800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>37900</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3800</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>6400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3150,8 +3208,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3236,8 +3297,8 @@
       <c r="AD29" s="3">
         <v>0</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3254,12 +3315,12 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL29" s="3">
         <v>-29000</v>
       </c>
-      <c r="AL29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AM29" s="3" t="s">
         <v>8</v>
       </c>
@@ -3272,8 +3333,11 @@
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3394,8 +3458,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3516,8 +3583,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3560,8 +3630,8 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R32" s="3">
         <v>0</v>
@@ -3638,130 +3708,136 @@
       <c r="AP32" s="3">
         <v>0</v>
       </c>
+      <c r="AQ32" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E33" s="3">
         <v>-47400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>31500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>122400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>185000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>96300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>190200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>284800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>344100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>258800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>350700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>451500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>404600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>333800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>384500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>738000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>987200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>639600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>442500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>613100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>497200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>172600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>139900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>85900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>78900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>8800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>41400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>78100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>66600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>35700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>52000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>73300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>23200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-42700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>39800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>37900</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3800</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>6400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3882,257 +3958,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E35" s="3">
         <v>-47400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>31500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>122400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>185000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>96300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>190200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>284800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>344100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>258800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>350700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>451500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>404600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>333800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>384500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>738000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>987200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>639600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>442500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>613100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>497200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>172600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>139900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>85900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>78900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>8800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>41400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>78100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>66600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>35700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>52000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>73300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>23200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-42700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>39800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>37900</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3800</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>6400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4175,8 +4260,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4219,130 +4305,134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>65700</v>
+      </c>
+      <c r="E41" s="3">
         <v>98300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>181800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>296200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>87000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>115400</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>153600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>328100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>75600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>697500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>66200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>88100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>89300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>144400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>80400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>85000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>166200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>281800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>42600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>224700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>90300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>19100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>423800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>340900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>385500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>163900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>14100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>43300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>10600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>11700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>10100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>34400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>13200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>10100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>57500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>9300</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4500</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>14400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4463,496 +4553,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1773900</v>
+      </c>
+      <c r="E43" s="3">
         <v>1699400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1524000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1702400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1760700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1683700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1658600</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1833200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1965900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1768500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1892900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2053500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2055100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1750700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1866800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2434000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2906700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2754300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2171500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2301600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2312000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1846500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>956500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>925500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>764800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>756800</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>692400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>770700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>769700</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>699800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>722800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>864700</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>891700</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>771200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>703200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>786100</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>773200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>666200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>625000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>725100</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1271800</v>
+      </c>
+      <c r="E44" s="3">
         <v>1189400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1094700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1176400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1309100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1348900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1212400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1203900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1289700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1356900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1228300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1331500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1362300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1336200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1426200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1758900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2065300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2188100</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1626200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1616600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2074400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1585600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>784500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>751100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>615100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>640000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>561300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>581500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>617500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>635500</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>596900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>679500</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>782800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>678800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>601500</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>627200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>651000</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>618000</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>541800</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>570600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>132500</v>
+      </c>
+      <c r="E45" s="3">
         <v>129000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>126800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>121200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>130900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>132400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>116700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>109200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>123500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>120500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>113400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>101000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>98600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>116100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>124200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>142300</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>139000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>155800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>128000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>88400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>438400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>119500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>58900</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>36100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>44100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>39100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>34600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>36200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>38800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>43900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>35400</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>39300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>43000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>33600</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>32900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>39300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>40900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>34800</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>29500</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>3243900</v>
+      </c>
+      <c r="E46" s="3">
         <v>3116100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2927300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>3296200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>3287600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>3280400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>3141200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3474400</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>3454700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>3943300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>3300700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3574100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>3605200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>3347300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>3497600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4420100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5277300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5379900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3968300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4231200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4915100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3570700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>2223700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>2061700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>1801600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>1604900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>1306900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>1430100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>1434000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>1385800</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>1373800</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>1614000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>1727000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>1503100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>1395900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>1455600</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>1470500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>1329600</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>1216000</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>1331000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,8 +5100,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -5073,252 +5178,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2720500</v>
+      </c>
+      <c r="E48" s="3">
         <v>2771700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2826400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2807900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2795000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2768300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2556000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2540300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2412800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2345900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2306000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2252600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2160200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2090300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2053300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1991700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1904300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1832900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1843300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1781000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1730600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1740200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1023700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1028900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1029900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1016700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1014600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>983100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>949300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>938700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>670100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>665700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>655600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>643700</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>639300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>641100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>643300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>644700</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>656100</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>669700</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>5198500</v>
+      </c>
+      <c r="E49" s="3">
         <v>5252800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>5321200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>5192300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>5251300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>5287300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>4782100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>4790000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>4773200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>4825200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4854700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4869900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4912200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4988400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>5007800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>5090700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4870500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4807900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4873600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4771000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3958000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>4038200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>905200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>898400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>903800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>909400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>897400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>856100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>835800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>839700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>843600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>851700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>859800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>866800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>873000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>879400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>886000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>892900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>899800</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>908300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5439,8 +5553,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5561,130 +5678,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>63500</v>
+      </c>
+      <c r="E52" s="3">
         <v>62300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>59100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>52600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>53300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>44100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>51000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>89400</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>80500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>54000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>38000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>40100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>55500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>50900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>36400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>35200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>33800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>29200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>26000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>22400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>30500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>21100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>25800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>29400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>30300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>30600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>28500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>30900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>35300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>44900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>62200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>80500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>96100</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>98000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>116900</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>130900</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>148800</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>138000</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>143300</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5805,130 +5928,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11323800</v>
+      </c>
+      <c r="E54" s="3">
         <v>11303100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11237500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11430900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11464600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11447600</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10583100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10894100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10721200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11168400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10499500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10736800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10733100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>10476900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>10595200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>11537700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>12085900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>12051200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10714300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10809100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10626100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>9379500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4173700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4014900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3764700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3561400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3249500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3297800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3250000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>3199500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2932300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>3193600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>3322900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>3109700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>3006100</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>3093000</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>3130700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>3015900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>2909900</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>3052300</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5971,8 +6100,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6015,740 +6145,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1032200</v>
+      </c>
+      <c r="E57" s="3">
         <v>924600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>714700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>960900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1008400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1022000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>868100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1021600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1028400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1025000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>881400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1032100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1062000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>938900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>803500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1088000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1265500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1563300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1093400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1004500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1318400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1123800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>600400</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>651300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>554400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>551500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>436800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>499400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>516900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>471300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>423200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>440400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>562500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>488200</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>514300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>505800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>503500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>467200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>409800</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>446600</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>124800</v>
+      </c>
+      <c r="E58" s="3">
         <v>135700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>125500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>121200</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>113200</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>111300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>107000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>105400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>99500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>100100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>101900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>102100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>104000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>105400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>6400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>3800</v>
-      </c>
-      <c r="S58" s="3">
-        <v>2900</v>
       </c>
       <c r="T58" s="3">
         <v>2900</v>
       </c>
       <c r="U58" s="3">
+        <v>2900</v>
+      </c>
+      <c r="V58" s="3">
         <v>3700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>3800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>11300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>14100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>27300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>29500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>24000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>22500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>13900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>14400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>28200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>33800</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>43400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>12500</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>24600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>45600</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>45700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>51800</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>59700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>175500</v>
+      </c>
+      <c r="E59" s="3">
         <v>180500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>168400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>184200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>182600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>194000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>168200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>194500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>218500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>198400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>205800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>254000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>241200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>323100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1032900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1201900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1260500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1116800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1031700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1024800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>923000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>723200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>447200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>404000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>354700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>284900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>370600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>350000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>318700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>249500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>292500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>303200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>250400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>187800</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>271600</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>251500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>265600</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>193000</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>293100</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>254300</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1813400</v>
+      </c>
+      <c r="E60" s="3">
         <v>1771900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1574900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1845100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1834600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1801500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1777300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1958900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1892500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1781500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1863400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2026700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1955900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1831900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1842800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2293700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2528800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2683100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2128700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2033200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2252700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1861200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1074900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1084900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>933100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>859000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>821300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>863700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>848200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>737900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>731300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>771800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>846800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>719400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>798400</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>781900</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>814800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>705900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>754700</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>760500</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5113400</v>
+      </c>
+      <c r="E61" s="3">
         <v>5156200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4974800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4959900</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5201300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4997900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4225900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4231900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4253300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4146100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3611500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3812200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4079600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3598200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2977800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3169400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3552400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3391600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2926100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2419700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2043800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1658100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1596900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1574100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1577900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1545200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1277400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1350500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1420500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1562100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1545700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1827000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1954200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1928400</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1771900</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1839100</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1887800</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1926600</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1785800</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1924800</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>153600</v>
+      </c>
+      <c r="E62" s="3">
         <v>141100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>157600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>137700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>134800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>136500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>135300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>135400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>130800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>125300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>125000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>120200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>123800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>141300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>812000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>849900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>868400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>840400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>857000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>832900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>847100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>876300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>349100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>348100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>337800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>323600</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>325800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>304500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>277200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>267000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>59000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>56500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>60400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>60900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>59600</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>60000</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>61000</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>58900</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>59700</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>66700</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6869,8 +7018,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6991,8 +7143,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7113,130 +7268,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7318600</v>
+      </c>
+      <c r="E66" s="3">
         <v>7298900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6885300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7114700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7286500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7073500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6286600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6447500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6416500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6211700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5767100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6156100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6391100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5819700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5632600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6313100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6949500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6915100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5911900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5285700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5143600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>4395600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3020900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3007100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2848700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2727800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2424500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2518800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2545800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2567000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2336000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2655300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2861400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2708700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2629900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2681000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2763600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2691400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2600300</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>2752000</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7279,8 +7440,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7401,8 +7563,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7523,8 +7688,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7645,8 +7813,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7767,130 +7938,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E72" s="3">
+      <c r="D72" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3">
         <v>153900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>122400</v>
       </c>
-      <c r="G72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H72" s="3">
+      <c r="H72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I72" s="3">
         <v>107600</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>24100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>179000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>53900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>699400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>460200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>318300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>91800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>409800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>703500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>970300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>890400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>893700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>540000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1267200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1232200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>735000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>562400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>422500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>336500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>257600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>248800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>207500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>137300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>70700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>35000</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>-17100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>-90400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>-147000</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>-171700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>-129000</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>-168700</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>-206700</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-219400</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>-225800</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8011,8 +8188,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8133,8 +8313,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8255,130 +8438,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4005200</v>
+      </c>
+      <c r="E76" s="3">
         <v>4004200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4352300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4316200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4178100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4374200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4296500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4446700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4304600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4956700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4732400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4580700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4342100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>4657200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>4962600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>5224600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>5136400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>5136000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>4802500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>5523400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>5482500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>4983900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>1152800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>1007900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>915900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>833500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>825000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>779000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>704100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>632500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>596300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>538300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>461500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>401000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>376200</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>412000</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>367100</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>324500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>309600</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>300300</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8499,257 +8688,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E81" s="3">
         <v>-47400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>31500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>122400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>185000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>96300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>190200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>284800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>344100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>258800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>350700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>451500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>404600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>333800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>384500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>738000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>987200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>639600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>442500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>613100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>497200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>172600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>139900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>85900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>78900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>8800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>41400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>78100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>66600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>35700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>52000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>73300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>56600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>23200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-42700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>39800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>37900</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3800</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>6400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>125500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8792,130 +8990,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>73600</v>
+      </c>
+      <c r="E83" s="3">
         <v>71700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>69300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>65100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>61700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>60500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>59300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>57100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>54200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>51900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>51600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>49000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>47800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>46200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>141700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>125700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>117900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>111900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>145900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>139900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>127200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>134300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>29300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>29400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>28500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>29400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>28300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>24400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>23800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>23600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>25200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>25100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>24800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>22800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>22200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>23000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>24200</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>23600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>22900</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>25600</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9036,8 +9238,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9158,8 +9363,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9280,8 +9488,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9402,8 +9613,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9524,130 +9738,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>68000</v>
+      </c>
+      <c r="E89" s="3">
         <v>87500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>194800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>547700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>341000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>132300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>373500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>730000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>452100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>317200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>611700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>649500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>391300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>654400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>971400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1500800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>947200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>179800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>840300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1107000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-3300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-200500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>104900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>-14700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>220500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-50700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>143800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>181500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>172700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>273300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>178500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>9400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>-178300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>186100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>68700</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>60100</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-136400</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>161900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>29100</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9690,130 +9910,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-38000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-46700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-88100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-85800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-88700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-100000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-99700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-99600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-88100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-93200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-99700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-145500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-125500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-105600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-134900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-85700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-50500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-67700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-61900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-59000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-39300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-28600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-28700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-26300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-28500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-34900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-23900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-21500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-22700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-28700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-29800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-20100</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-14300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-23500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-14800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-9800</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>25600</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-45600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9934,8 +10158,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10056,130 +10283,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-49300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-57800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-305200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-102500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-147400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-912100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-175800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-219300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-164600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-151000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-192200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-164300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-133000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-178900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-140100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-510200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-258800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-48300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-374200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-799100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-302700</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>131400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-40100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-26900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-25400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-43900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-92800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-65600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-20000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-20800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-19900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-29300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-19500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-16200</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-20700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-13200</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-9300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-3000</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-9600</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10222,8 +10455,9 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10266,8 +10500,8 @@
       <c r="P96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10344,8 +10578,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10466,8 +10703,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10588,8 +10828,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10710,130 +10953,136 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-51500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-113000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-236100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-222000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>741500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-372100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-258200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-909400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>465200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-441400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-486400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-313500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-411600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-835800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-1071800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-804100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>107700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-648200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-173400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>377200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-335600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>18100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>26400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>244300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-80200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-83100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-153900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-277800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-129300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>150400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-121800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-45600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-44400</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>135800</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-184700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>14500</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10876,8 +11125,8 @@
       <c r="P101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q101" s="3">
-        <v>0</v>
+      <c r="Q101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R101" s="3">
         <v>0</v>
@@ -10954,126 +11203,132 @@
       <c r="AP101" s="3">
         <v>0</v>
       </c>
+      <c r="AQ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-32700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-83400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-114400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>209100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-28400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-38300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-174500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>252500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-621900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>631300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-21900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-1200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-55100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>64000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-4500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-81200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-115600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>239200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-182100</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>134500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>71100</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-404700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>82900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-44500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>221600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>149800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-29200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>32700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-24300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>21300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-47500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>48200</v>
-      </c>
-      <c r="AL102" s="3">
-        <v>2400</v>
       </c>
       <c r="AM102" s="3">
         <v>2400</v>
       </c>
       <c r="AN102" s="3">
+        <v>2400</v>
+      </c>
+      <c r="AO102" s="3">
         <v>-9900</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>8600</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-300</v>
       </c>
     </row>
